--- a/Result/profitability/3171.xlsx
+++ b/Result/profitability/3171.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8612500000000001</v>
+        <v>1.075</v>
       </c>
       <c r="N2" t="n">
-        <v>27.915</v>
+        <v>27.56</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7775</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>27.0375</v>
+        <v>26.5725</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.72375</v>
+        <v>0.91625</v>
       </c>
       <c r="N4" t="n">
-        <v>26.98</v>
+        <v>26.49</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6224999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="N5" t="n">
-        <v>26.6575</v>
+        <v>26.04</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.495</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>27.235</v>
+        <v>27.30625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3225</v>
+        <v>0.46625</v>
       </c>
       <c r="N7" t="n">
-        <v>27.92625</v>
+        <v>27.89375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,13 +1393,13 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20375</v>
+        <v>0.3175</v>
       </c>
       <c r="N8" t="n">
-        <v>29.97</v>
+        <v>29.85375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1411,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.015</v>
+        <v>0.01500000000000005</v>
       </c>
       <c r="N9" t="n">
         <v>29.65</v>
@@ -1649,7 +1649,7 @@
         <v>-0.08</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01375</v>
+        <v>0.01375000000000006</v>
       </c>
       <c r="N10" t="n">
         <v>29.17375</v>
@@ -1776,7 +1776,7 @@
         <v>-0.08</v>
       </c>
       <c r="M11" t="n">
-        <v>0.007500000000000001</v>
+        <v>0.007500000000000057</v>
       </c>
       <c r="N11" t="n">
         <v>29.94625</v>
@@ -1903,7 +1903,7 @@
         <v>-0.16</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03</v>
+        <v>-0.02999999999999994</v>
       </c>
       <c r="N12" t="n">
         <v>29.77875</v>
@@ -2030,7 +2030,7 @@
         <v>-0.54</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0975</v>
+        <v>-0.09749999999999995</v>
       </c>
       <c r="N13" t="n">
         <v>28.69625</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>800</v>
+      </c>
+      <c r="D75" t="n">
+        <v>601</v>
+      </c>
+      <c r="E75" t="n">
+        <v>199</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>95</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>95</v>
+      </c>
+      <c r="K75" t="n">
+        <v>71</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.16375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.835</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6319444444444446</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9300000000000033</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03610248447204978</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.238095238095238</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.940000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.165938864628821</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
